--- a/result/train_info_group_part_detrend_plr_stft_bin_win.xlsx
+++ b/result/train_info_group_part_detrend_plr_stft_bin_win.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
@@ -467,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.857705354690552</v>
+        <v>5.242045879364014</v>
       </c>
       <c r="C2" t="n">
         <v>0.9346139637975619</v>
@@ -489,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.20287370681763</v>
+        <v>21.79190230369568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.992584352984798</v>
+        <v>0.9929525222551929</v>
       </c>
       <c r="D3" t="n">
         <v>0.9922164566345441</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9924003707136237</v>
+        <v>0.992584352984798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9925678186547752</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0478057861328125</v>
+        <v>0.004001140594482422</v>
       </c>
       <c r="C4" t="n">
         <v>0.9981481481481481</v>
@@ -533,19 +521,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.598246574401855</v>
+        <v>1.704240560531616</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7995537374488657</v>
+        <v>0.7994791666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7968865826538176</v>
+        <v>0.7965159377316531</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7982179320586598</v>
+        <v>0.7979948013367991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7980304719435154</v>
+        <v>0.7978446674098848</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +543,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.004650115966797</v>
+        <v>124.3377261161804</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9642593957258658</v>
+        <v>0.9642725598526704</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9699777613046702</v>
+        <v>0.9703484062268347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9671101256467111</v>
+        <v>0.9673009421762424</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9669267930137495</v>
+        <v>0.9671125975473801</v>
       </c>
     </row>
   </sheetData>
